--- a/artfynd/A 7536-2022 artfynd.xlsx
+++ b/artfynd/A 7536-2022 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 7536-2022 artfynd.xlsx
+++ b/artfynd/A 7536-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123922938</v>
+        <v>123922888</v>
       </c>
       <c r="B2" t="n">
-        <v>58158</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,14 +708,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3K</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598093</v>
+        <v>598169</v>
       </c>
       <c r="R2" t="n">
-        <v>6610334</v>
+        <v>6610336</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mot S</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,6 +798,490 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125445155</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58463</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Odlingen, Odlingen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>598152</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6610359</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kungsåra</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Revir nr 2</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125445313</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Odlingen, Odlingen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>598152</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6610359</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kungsåra</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123922938</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Odlingen, Odlingen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>598093</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6610334</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kungsåra</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125444635</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nytorp, Nytorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>598109</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6610493</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kungsåra</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7536-2022 artfynd.xlsx
+++ b/artfynd/A 7536-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123922888</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125445155</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1040,6 +1055,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125445313</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1161,6 +1181,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123922938</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1282,8 +1307,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125444635</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>